--- a/output/estat-desc.xlsx
+++ b/output/estat-desc.xlsx
@@ -401,10 +401,10 @@
         <v>3170</v>
       </c>
       <c r="C2">
-        <v>387.1016018289494</v>
+        <v>279.9332529577512</v>
       </c>
       <c r="D2">
-        <v>387.1268169634347</v>
+        <v>279.9584680922365</v>
       </c>
       <c r="E2">
         <v>1.18230522900363</v>
@@ -426,10 +426,10 @@
         <v>3072</v>
       </c>
       <c r="C3">
-        <v>387.5687990774547</v>
+        <v>282.7778769394109</v>
       </c>
       <c r="D3">
-        <v>387.5917350937759</v>
+        <v>282.8008129557321</v>
       </c>
       <c r="E3">
         <v>1.536246302957206</v>
@@ -451,10 +451,10 @@
         <v>2256</v>
       </c>
       <c r="C4">
-        <v>387.1826566112436</v>
+        <v>284.7691612063542</v>
       </c>
       <c r="D4">
-        <v>387.2390567885702</v>
+        <v>284.8255613836808</v>
       </c>
       <c r="E4">
         <v>1.215865786736222</v>
@@ -476,10 +476,10 @@
         <v>2715</v>
       </c>
       <c r="C5">
-        <v>386.9414880307917</v>
+        <v>286.9054193590567</v>
       </c>
       <c r="D5">
-        <v>386.9838668866848</v>
+        <v>286.9477982149498</v>
       </c>
       <c r="E5">
         <v>1.625165666039994</v>
@@ -501,10 +501,10 @@
         <v>2718</v>
       </c>
       <c r="C6">
-        <v>387.2625050464738</v>
+        <v>289.6038631078932</v>
       </c>
       <c r="D6">
-        <v>387.3690273265964</v>
+        <v>289.7103853880158</v>
       </c>
       <c r="E6">
         <v>1.392900313456778</v>
@@ -526,10 +526,10 @@
         <v>2629</v>
       </c>
       <c r="C7">
-        <v>386.8173255130815</v>
+        <v>291.5361103076553</v>
       </c>
       <c r="D7">
-        <v>386.8964301981485</v>
+        <v>291.6152149927223</v>
       </c>
       <c r="E7">
         <v>1.752316074368826</v>
@@ -551,10 +551,10 @@
         <v>2809</v>
       </c>
       <c r="C8">
-        <v>387.439487283573</v>
+        <v>294.5356988113012</v>
       </c>
       <c r="D8">
-        <v>387.6035205697006</v>
+        <v>294.6997320974289</v>
       </c>
       <c r="E8">
         <v>1.539506506405061</v>
@@ -576,10 +576,10 @@
         <v>1215</v>
       </c>
       <c r="C9">
-        <v>387.4388173465784</v>
+        <v>296.912455607461</v>
       </c>
       <c r="D9">
-        <v>387.5365936072684</v>
+        <v>297.010231868151</v>
       </c>
       <c r="E9">
         <v>1.620785703530477</v>
@@ -601,10 +601,10 @@
         <v>1937</v>
       </c>
       <c r="C10">
-        <v>386.9694360693297</v>
+        <v>298.8205010633667</v>
       </c>
       <c r="D10">
-        <v>386.9888011663205</v>
+        <v>298.8398661603575</v>
       </c>
       <c r="E10">
         <v>1.506517856368988</v>
@@ -626,19 +626,19 @@
         <v>1838</v>
       </c>
       <c r="C11">
-        <v>387.1909790238212</v>
+        <v>280.3757517511818</v>
       </c>
       <c r="D11">
-        <v>387.3076946489816</v>
+        <v>280.3333307631349</v>
       </c>
       <c r="E11">
-        <v>1.192266613200502</v>
+        <v>1.055021906385138</v>
       </c>
       <c r="F11">
-        <v>-0.6937070539837423</v>
+        <v>0.06436021561279559</v>
       </c>
       <c r="G11">
-        <v>1.380739891101147</v>
+        <v>1.803687756459474</v>
       </c>
     </row>
     <row r="12">
@@ -651,19 +651,19 @@
         <v>1885</v>
       </c>
       <c r="C12">
-        <v>387.5317655884826</v>
+        <v>282.8959752744059</v>
       </c>
       <c r="D12">
-        <v>387.6479332138931</v>
+        <v>282.9398052653024</v>
       </c>
       <c r="E12">
-        <v>1.333573253186748</v>
+        <v>1.237620171297899</v>
       </c>
       <c r="F12">
-        <v>-0.2459064695264767</v>
+        <v>-0.04593991246720935</v>
       </c>
       <c r="G12">
-        <v>0.2357726206422357</v>
+        <v>0.6299176083247549</v>
       </c>
     </row>
     <row r="13">
@@ -676,19 +676,19 @@
         <v>1167</v>
       </c>
       <c r="C13">
-        <v>387.345868595697</v>
+        <v>285.1972107874744</v>
       </c>
       <c r="D13">
-        <v>387.4181034194296</v>
+        <v>285.1648558172746</v>
       </c>
       <c r="E13">
-        <v>1.463258557030148</v>
+        <v>1.25239397599231</v>
       </c>
       <c r="F13">
-        <v>-0.4569013605566123</v>
+        <v>0.0723337324400065</v>
       </c>
       <c r="G13">
-        <v>0.9812587943120659</v>
+        <v>0.2627288831383043</v>
       </c>
     </row>
     <row r="14">
@@ -701,19 +701,19 @@
         <v>1332</v>
       </c>
       <c r="C14">
-        <v>387.1412462094812</v>
+        <v>287.4318059853192</v>
       </c>
       <c r="D14">
-        <v>387.217081261914</v>
+        <v>287.3808884249108</v>
       </c>
       <c r="E14">
-        <v>1.432882181232127</v>
+        <v>1.182145250418453</v>
       </c>
       <c r="F14">
-        <v>-0.4359629151490947</v>
+        <v>0.01363957829692552</v>
       </c>
       <c r="G14">
-        <v>0.7483782737744353</v>
+        <v>1.072396971455331</v>
       </c>
     </row>
     <row r="15">
@@ -726,19 +726,19 @@
         <v>1477</v>
       </c>
       <c r="C15">
-        <v>388.4381883895534</v>
+        <v>290.8729051175421</v>
       </c>
       <c r="D15">
-        <v>388.4803554515964</v>
+        <v>290.8403597532501</v>
       </c>
       <c r="E15">
-        <v>1.445688955703633</v>
+        <v>1.287211175088933</v>
       </c>
       <c r="F15">
-        <v>-0.5779276682639747</v>
+        <v>-0.03100497647199536</v>
       </c>
       <c r="G15">
-        <v>2.11375978505539</v>
+        <v>1.037000102781211</v>
       </c>
     </row>
     <row r="16">
@@ -751,19 +751,19 @@
         <v>856</v>
       </c>
       <c r="C16">
-        <v>388.4124658794146</v>
+        <v>293.247900116503</v>
       </c>
       <c r="D16">
-        <v>388.479071799711</v>
+        <v>293.2388264429176</v>
       </c>
       <c r="E16">
-        <v>1.587305773226825</v>
+        <v>1.480613552657666</v>
       </c>
       <c r="F16">
-        <v>-0.1581859639359714</v>
+        <v>-0.05884388783364015</v>
       </c>
       <c r="G16">
-        <v>0.1198330976075468</v>
+        <v>0.2233034021745803</v>
       </c>
     </row>
     <row r="17">
@@ -776,19 +776,19 @@
         <v>1445</v>
       </c>
       <c r="C17">
-        <v>387.7634293206705</v>
+        <v>295.017587537937</v>
       </c>
       <c r="D17">
-        <v>387.6771289681381</v>
+        <v>294.9492438161789</v>
       </c>
       <c r="E17">
-        <v>1.69418452977483</v>
+        <v>1.602447759903844</v>
       </c>
       <c r="F17">
-        <v>0.3939887492320298</v>
+        <v>0.4619773738876483</v>
       </c>
       <c r="G17">
-        <v>0.152294289086699</v>
+        <v>0.1861982777992561</v>
       </c>
     </row>
     <row r="18">
@@ -801,19 +801,19 @@
         <v>1747</v>
       </c>
       <c r="C18">
-        <v>387.1302126342749</v>
+        <v>296.7045547178555</v>
       </c>
       <c r="D18">
-        <v>387.1716338904715</v>
+        <v>296.6655663408072</v>
       </c>
       <c r="E18">
-        <v>1.351063952638233</v>
+        <v>1.209097355889812</v>
       </c>
       <c r="F18">
-        <v>-0.1214769430852471</v>
+        <v>0.4955264217789787</v>
       </c>
       <c r="G18">
-        <v>2.089503294318475</v>
+        <v>1.706808091618661</v>
       </c>
     </row>
     <row r="19">
@@ -826,10 +826,10 @@
         <v>1408</v>
       </c>
       <c r="C19">
-        <v>387.9329004408691</v>
+        <v>299.7839654349061</v>
       </c>
       <c r="D19">
-        <v>387.8003093450315</v>
+        <v>299.6513743390685</v>
       </c>
       <c r="E19">
         <v>1.338840305557669</v>

--- a/output/estat-desc.xlsx
+++ b/output/estat-desc.xlsx
@@ -401,10 +401,10 @@
         <v>3170</v>
       </c>
       <c r="C2">
-        <v>279.9332529577512</v>
+        <v>387.1016018289494</v>
       </c>
       <c r="D2">
-        <v>279.9584680922365</v>
+        <v>387.1268169634347</v>
       </c>
       <c r="E2">
         <v>1.18230522900363</v>
@@ -426,10 +426,10 @@
         <v>3072</v>
       </c>
       <c r="C3">
-        <v>282.7778769394109</v>
+        <v>387.5687990774547</v>
       </c>
       <c r="D3">
-        <v>282.8008129557321</v>
+        <v>387.5917350937759</v>
       </c>
       <c r="E3">
         <v>1.536246302957206</v>
@@ -451,10 +451,10 @@
         <v>2256</v>
       </c>
       <c r="C4">
-        <v>284.7691612063542</v>
+        <v>387.1826566112436</v>
       </c>
       <c r="D4">
-        <v>284.8255613836808</v>
+        <v>387.2390567885702</v>
       </c>
       <c r="E4">
         <v>1.215865786736222</v>
@@ -476,10 +476,10 @@
         <v>2715</v>
       </c>
       <c r="C5">
-        <v>286.9054193590567</v>
+        <v>386.9414880307917</v>
       </c>
       <c r="D5">
-        <v>286.9477982149498</v>
+        <v>386.9838668866848</v>
       </c>
       <c r="E5">
         <v>1.625165666039994</v>
@@ -501,10 +501,10 @@
         <v>2718</v>
       </c>
       <c r="C6">
-        <v>289.6038631078932</v>
+        <v>387.2625050464738</v>
       </c>
       <c r="D6">
-        <v>289.7103853880158</v>
+        <v>387.3690273265964</v>
       </c>
       <c r="E6">
         <v>1.392900313456778</v>
@@ -526,10 +526,10 @@
         <v>2629</v>
       </c>
       <c r="C7">
-        <v>291.5361103076553</v>
+        <v>386.8173255130815</v>
       </c>
       <c r="D7">
-        <v>291.6152149927223</v>
+        <v>386.8964301981485</v>
       </c>
       <c r="E7">
         <v>1.752316074368826</v>
@@ -551,10 +551,10 @@
         <v>2809</v>
       </c>
       <c r="C8">
-        <v>294.5356988113012</v>
+        <v>387.439487283573</v>
       </c>
       <c r="D8">
-        <v>294.6997320974289</v>
+        <v>387.6035205697006</v>
       </c>
       <c r="E8">
         <v>1.539506506405061</v>
@@ -576,10 +576,10 @@
         <v>1215</v>
       </c>
       <c r="C9">
-        <v>296.912455607461</v>
+        <v>387.4388173465784</v>
       </c>
       <c r="D9">
-        <v>297.010231868151</v>
+        <v>387.5365936072684</v>
       </c>
       <c r="E9">
         <v>1.620785703530477</v>
@@ -601,10 +601,10 @@
         <v>1937</v>
       </c>
       <c r="C10">
-        <v>298.8205010633667</v>
+        <v>386.9694360693297</v>
       </c>
       <c r="D10">
-        <v>298.8398661603575</v>
+        <v>386.9888011663205</v>
       </c>
       <c r="E10">
         <v>1.506517856368988</v>
@@ -626,19 +626,19 @@
         <v>1838</v>
       </c>
       <c r="C11">
-        <v>280.3757517511818</v>
+        <v>387.1909790238212</v>
       </c>
       <c r="D11">
-        <v>280.3333307631349</v>
+        <v>387.3076946489816</v>
       </c>
       <c r="E11">
-        <v>1.055021906385138</v>
+        <v>1.192266613200502</v>
       </c>
       <c r="F11">
-        <v>0.06436021561279559</v>
+        <v>-0.6937070539837423</v>
       </c>
       <c r="G11">
-        <v>1.803687756459474</v>
+        <v>1.380739891101147</v>
       </c>
     </row>
     <row r="12">
@@ -651,19 +651,19 @@
         <v>1885</v>
       </c>
       <c r="C12">
-        <v>282.8959752744059</v>
+        <v>387.5317655884826</v>
       </c>
       <c r="D12">
-        <v>282.9398052653024</v>
+        <v>387.6479332138931</v>
       </c>
       <c r="E12">
-        <v>1.237620171297899</v>
+        <v>1.333573253186748</v>
       </c>
       <c r="F12">
-        <v>-0.04593991246720935</v>
+        <v>-0.2459064695264767</v>
       </c>
       <c r="G12">
-        <v>0.6299176083247549</v>
+        <v>0.2357726206422357</v>
       </c>
     </row>
     <row r="13">
@@ -676,19 +676,19 @@
         <v>1167</v>
       </c>
       <c r="C13">
-        <v>285.1972107874744</v>
+        <v>387.345868595697</v>
       </c>
       <c r="D13">
-        <v>285.1648558172746</v>
+        <v>387.4181034194296</v>
       </c>
       <c r="E13">
-        <v>1.25239397599231</v>
+        <v>1.463258557030148</v>
       </c>
       <c r="F13">
-        <v>0.0723337324400065</v>
+        <v>-0.4569013605566123</v>
       </c>
       <c r="G13">
-        <v>0.2627288831383043</v>
+        <v>0.9812587943120659</v>
       </c>
     </row>
     <row r="14">
@@ -701,19 +701,19 @@
         <v>1332</v>
       </c>
       <c r="C14">
-        <v>287.4318059853192</v>
+        <v>387.1412462094812</v>
       </c>
       <c r="D14">
-        <v>287.3808884249108</v>
+        <v>387.217081261914</v>
       </c>
       <c r="E14">
-        <v>1.182145250418453</v>
+        <v>1.432882181232127</v>
       </c>
       <c r="F14">
-        <v>0.01363957829692552</v>
+        <v>-0.4359629151490947</v>
       </c>
       <c r="G14">
-        <v>1.072396971455331</v>
+        <v>0.7483782737744353</v>
       </c>
     </row>
     <row r="15">
@@ -726,19 +726,19 @@
         <v>1477</v>
       </c>
       <c r="C15">
-        <v>290.8729051175421</v>
+        <v>388.4381883895534</v>
       </c>
       <c r="D15">
-        <v>290.8403597532501</v>
+        <v>388.4803554515964</v>
       </c>
       <c r="E15">
-        <v>1.287211175088933</v>
+        <v>1.445688955703633</v>
       </c>
       <c r="F15">
-        <v>-0.03100497647199536</v>
+        <v>-0.5779276682639747</v>
       </c>
       <c r="G15">
-        <v>1.037000102781211</v>
+        <v>2.11375978505539</v>
       </c>
     </row>
     <row r="16">
@@ -751,19 +751,19 @@
         <v>856</v>
       </c>
       <c r="C16">
-        <v>293.247900116503</v>
+        <v>388.4124658794146</v>
       </c>
       <c r="D16">
-        <v>293.2388264429176</v>
+        <v>388.479071799711</v>
       </c>
       <c r="E16">
-        <v>1.480613552657666</v>
+        <v>1.587305773226825</v>
       </c>
       <c r="F16">
-        <v>-0.05884388783364015</v>
+        <v>-0.1581859639359714</v>
       </c>
       <c r="G16">
-        <v>0.2233034021745803</v>
+        <v>0.1198330976075468</v>
       </c>
     </row>
     <row r="17">
@@ -776,19 +776,19 @@
         <v>1445</v>
       </c>
       <c r="C17">
-        <v>295.017587537937</v>
+        <v>387.7634293206705</v>
       </c>
       <c r="D17">
-        <v>294.9492438161789</v>
+        <v>387.6771289681381</v>
       </c>
       <c r="E17">
-        <v>1.602447759903844</v>
+        <v>1.69418452977483</v>
       </c>
       <c r="F17">
-        <v>0.4619773738876483</v>
+        <v>0.3939887492320298</v>
       </c>
       <c r="G17">
-        <v>0.1861982777992561</v>
+        <v>0.152294289086699</v>
       </c>
     </row>
     <row r="18">
@@ -801,19 +801,19 @@
         <v>1747</v>
       </c>
       <c r="C18">
-        <v>296.7045547178555</v>
+        <v>387.1302126342749</v>
       </c>
       <c r="D18">
-        <v>296.6655663408072</v>
+        <v>387.1716338904715</v>
       </c>
       <c r="E18">
-        <v>1.209097355889812</v>
+        <v>1.351063952638233</v>
       </c>
       <c r="F18">
-        <v>0.4955264217789787</v>
+        <v>-0.1214769430852471</v>
       </c>
       <c r="G18">
-        <v>1.706808091618661</v>
+        <v>2.089503294318475</v>
       </c>
     </row>
     <row r="19">
@@ -826,10 +826,10 @@
         <v>1408</v>
       </c>
       <c r="C19">
-        <v>299.7839654349061</v>
+        <v>387.9329004408691</v>
       </c>
       <c r="D19">
-        <v>299.6513743390685</v>
+        <v>387.8003093450315</v>
       </c>
       <c r="E19">
         <v>1.338840305557669</v>
